--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/183.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/183.xlsx
@@ -426,13 +426,13 @@
         <v>-4.404623982764865</v>
       </c>
       <c r="E2">
-        <v>-14.13982705858172</v>
+        <v>-12.59865602802528</v>
       </c>
       <c r="F2">
-        <v>1.792216783089833</v>
+        <v>0.8955193263561874</v>
       </c>
       <c r="G2">
-        <v>-8.171715343804401</v>
+        <v>-8.051214796720467</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.148827537160725</v>
       </c>
       <c r="E3">
-        <v>-14.59642856430112</v>
+        <v>-11.23460720133085</v>
       </c>
       <c r="F3">
-        <v>2.156331361226263</v>
+        <v>0.713692466498669</v>
       </c>
       <c r="G3">
-        <v>-8.520775954919614</v>
+        <v>-7.655707231689279</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.907746950046955</v>
       </c>
       <c r="E4">
-        <v>-15.69898518789664</v>
+        <v>-11.79038228781822</v>
       </c>
       <c r="F4">
-        <v>1.812187314683525</v>
+        <v>1.190061703627362</v>
       </c>
       <c r="G4">
-        <v>-8.23840297314748</v>
+        <v>-6.396561099100718</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.699189144266413</v>
       </c>
       <c r="E5">
-        <v>-15.19418713331361</v>
+        <v>-13.35486590256615</v>
       </c>
       <c r="F5">
-        <v>2.069629797179615</v>
+        <v>1.28874400292431</v>
       </c>
       <c r="G5">
-        <v>-7.078381195095776</v>
+        <v>-7.138374901358449</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.501952116049765</v>
       </c>
       <c r="E6">
-        <v>-16.33691132135716</v>
+        <v>-14.85281717719339</v>
       </c>
       <c r="F6">
-        <v>2.003779305215643</v>
+        <v>0.5539994805153323</v>
       </c>
       <c r="G6">
-        <v>-6.249907242256544</v>
+        <v>-6.574691622932283</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.302684733370537</v>
       </c>
       <c r="E7">
-        <v>-16.41348328835286</v>
+        <v>-15.43982514891167</v>
       </c>
       <c r="F7">
-        <v>2.350686918580823</v>
+        <v>0.750516796444467</v>
       </c>
       <c r="G7">
-        <v>-5.944870265722558</v>
+        <v>-5.425405944064437</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.090451445999814</v>
       </c>
       <c r="E8">
-        <v>-17.02773003122728</v>
+        <v>-16.17990459903722</v>
       </c>
       <c r="F8">
-        <v>2.322748762526555</v>
+        <v>1.137023392519295</v>
       </c>
       <c r="G8">
-        <v>-6.096615741606131</v>
+        <v>-5.518035008253245</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.860916724364182</v>
       </c>
       <c r="E9">
-        <v>-18.24036932947525</v>
+        <v>-15.61724623205819</v>
       </c>
       <c r="F9">
-        <v>2.655865464780089</v>
+        <v>0.7264856428835889</v>
       </c>
       <c r="G9">
-        <v>-5.494834705114032</v>
+        <v>-4.57542006631102</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.60818832643345</v>
       </c>
       <c r="E10">
-        <v>-17.94158514292317</v>
+        <v>-17.16995128591217</v>
       </c>
       <c r="F10">
-        <v>2.51852648779318</v>
+        <v>1.099285264260288</v>
       </c>
       <c r="G10">
-        <v>-4.576638347069473</v>
+        <v>-6.378515315366151</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.340506803064465</v>
       </c>
       <c r="E11">
-        <v>-20.78993642358572</v>
+        <v>-17.55062839641896</v>
       </c>
       <c r="F11">
-        <v>2.736941705415096</v>
+        <v>1.478791880188874</v>
       </c>
       <c r="G11">
-        <v>-4.872673950282181</v>
+        <v>-4.238015886039579</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.066406167137755</v>
       </c>
       <c r="E12">
-        <v>-20.00009810106389</v>
+        <v>-18.98390853374266</v>
       </c>
       <c r="F12">
-        <v>2.71502479925133</v>
+        <v>0.9958819376294161</v>
       </c>
       <c r="G12">
-        <v>-4.317263725158654</v>
+        <v>-4.330793924777654</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.796966079627363</v>
       </c>
       <c r="E13">
-        <v>-20.93865603847162</v>
+        <v>-18.84946266892894</v>
       </c>
       <c r="F13">
-        <v>3.043136990812074</v>
+        <v>1.492897948777693</v>
       </c>
       <c r="G13">
-        <v>-3.495914066319933</v>
+        <v>-2.990373899199987</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.551713579366486</v>
       </c>
       <c r="E14">
-        <v>-22.91149479686123</v>
+        <v>-20.45579844045576</v>
       </c>
       <c r="F14">
-        <v>3.092311059486469</v>
+        <v>1.908972334293776</v>
       </c>
       <c r="G14">
-        <v>-3.632616423273058</v>
+        <v>-2.359360745596124</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.341244556294143</v>
       </c>
       <c r="E15">
-        <v>-23.01175973986506</v>
+        <v>-21.30708815526168</v>
       </c>
       <c r="F15">
-        <v>3.878400911379909</v>
+        <v>1.871269047564909</v>
       </c>
       <c r="G15">
-        <v>-3.264920751317285</v>
+        <v>-3.245620270823335</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.17051401513891</v>
       </c>
       <c r="E16">
-        <v>-23.39982731995237</v>
+        <v>-22.4525113138138</v>
       </c>
       <c r="F16">
-        <v>4.367164231002831</v>
+        <v>2.485192645685011</v>
       </c>
       <c r="G16">
-        <v>-2.773225285642572</v>
+        <v>-1.861474559762972</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.042183548046059</v>
       </c>
       <c r="E17">
-        <v>-25.22743338844198</v>
+        <v>-22.69018827210638</v>
       </c>
       <c r="F17">
-        <v>4.197535074106027</v>
+        <v>2.623477095103437</v>
       </c>
       <c r="G17">
-        <v>-2.374261511068383</v>
+        <v>-3.035933626911437</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.9498432299559245</v>
       </c>
       <c r="E18">
-        <v>-25.98357533587274</v>
+        <v>-23.5858162759214</v>
       </c>
       <c r="F18">
-        <v>4.729069539387223</v>
+        <v>2.918141417730101</v>
       </c>
       <c r="G18">
-        <v>-3.024350028069527</v>
+        <v>-2.578803567212253</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.8902733791632188</v>
       </c>
       <c r="E19">
-        <v>-26.99462961366927</v>
+        <v>-25.25670997290157</v>
       </c>
       <c r="F19">
-        <v>5.051646678773507</v>
+        <v>3.093460829981078</v>
       </c>
       <c r="G19">
-        <v>-2.577356858811592</v>
+        <v>-1.937941540629059</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.8639835207535537</v>
       </c>
       <c r="E20">
-        <v>-27.0133050404769</v>
+        <v>-25.24478197236537</v>
       </c>
       <c r="F20">
-        <v>5.151977615928426</v>
+        <v>3.44869873646147</v>
       </c>
       <c r="G20">
-        <v>-2.570451060816672</v>
+        <v>-1.72149145218043</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.8678048384693179</v>
       </c>
       <c r="E21">
-        <v>-27.61623512680615</v>
+        <v>-24.06066753189171</v>
       </c>
       <c r="F21">
-        <v>5.850181291750469</v>
+        <v>3.955931234470247</v>
       </c>
       <c r="G21">
-        <v>-2.174801142327294</v>
+        <v>-2.034073161998415</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.9064628130867631</v>
       </c>
       <c r="E22">
-        <v>-28.45701878191428</v>
+        <v>-26.47230183620255</v>
       </c>
       <c r="F22">
-        <v>5.277747621203051</v>
+        <v>3.744036134102195</v>
       </c>
       <c r="G22">
-        <v>-2.428710053552776</v>
+        <v>-1.409379839829021</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.9838912921774794</v>
       </c>
       <c r="E23">
-        <v>-28.63209864399883</v>
+        <v>-26.6466118577058</v>
       </c>
       <c r="F23">
-        <v>5.48478866294028</v>
+        <v>4.107830803643706</v>
       </c>
       <c r="G23">
-        <v>-2.787804928197522</v>
+        <v>-2.321640389721668</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.09894017803113</v>
       </c>
       <c r="E24">
-        <v>-28.86214059511447</v>
+        <v>-26.73927802132475</v>
       </c>
       <c r="F24">
-        <v>5.254503569482146</v>
+        <v>3.519153061521624</v>
       </c>
       <c r="G24">
-        <v>-2.695430776015238</v>
+        <v>-1.205556172067172</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.255631144311562</v>
       </c>
       <c r="E25">
-        <v>-28.26522885074142</v>
+        <v>-29.40337022308921</v>
       </c>
       <c r="F25">
-        <v>5.59299220220085</v>
+        <v>3.697099841886316</v>
       </c>
       <c r="G25">
-        <v>-2.211061547618931</v>
+        <v>-3.237231348426821</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.45201369261155</v>
       </c>
       <c r="E26">
-        <v>-29.6091735170788</v>
+        <v>-27.12271750097623</v>
       </c>
       <c r="F26">
-        <v>5.798994332857551</v>
+        <v>4.063379346009151</v>
       </c>
       <c r="G26">
-        <v>-2.563104960265029</v>
+        <v>-2.460160236175853</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.681312011094194</v>
       </c>
       <c r="E27">
-        <v>-28.75085787484998</v>
+        <v>-27.90650578222381</v>
       </c>
       <c r="F27">
-        <v>5.44166910198061</v>
+        <v>3.817388640987604</v>
       </c>
       <c r="G27">
-        <v>-2.601262308150669</v>
+        <v>-1.430113786541476</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.941397235600089</v>
       </c>
       <c r="E28">
-        <v>-28.94012544600056</v>
+        <v>-27.36062088296919</v>
       </c>
       <c r="F28">
-        <v>5.440284943010516</v>
+        <v>3.496008783273393</v>
       </c>
       <c r="G28">
-        <v>-2.395051737055006</v>
+        <v>-2.982971519374176</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.223359997948784</v>
       </c>
       <c r="E29">
-        <v>-28.86867518310754</v>
+        <v>-26.27094776792549</v>
       </c>
       <c r="F29">
-        <v>5.194058265807568</v>
+        <v>4.261491453795134</v>
       </c>
       <c r="G29">
-        <v>-2.690398746795546</v>
+        <v>-2.7433012645131</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.518042068792381</v>
       </c>
       <c r="E30">
-        <v>-27.63100700901917</v>
+        <v>-27.46245720645368</v>
       </c>
       <c r="F30">
-        <v>5.090509238232475</v>
+        <v>3.705202081349705</v>
       </c>
       <c r="G30">
-        <v>-2.549323159185044</v>
+        <v>-2.215097102631303</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.82120617260555</v>
       </c>
       <c r="E31">
-        <v>-28.09174301150757</v>
+        <v>-26.76626319793646</v>
       </c>
       <c r="F31">
-        <v>5.495263293864997</v>
+        <v>3.904454457394803</v>
       </c>
       <c r="G31">
-        <v>-2.331502504883157</v>
+        <v>-2.20525154019751</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.123108413749985</v>
       </c>
       <c r="E32">
-        <v>-26.69448235644088</v>
+        <v>-25.53281556162324</v>
       </c>
       <c r="F32">
-        <v>5.223716326486002</v>
+        <v>4.019453678738524</v>
       </c>
       <c r="G32">
-        <v>-2.66139836787153</v>
+        <v>-2.382696781102446</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.418168262678437</v>
       </c>
       <c r="E33">
-        <v>-26.77280684287755</v>
+        <v>-25.95078012710919</v>
       </c>
       <c r="F33">
-        <v>4.740138060030229</v>
+        <v>3.051883798583046</v>
       </c>
       <c r="G33">
-        <v>-2.59344279958691</v>
+        <v>-2.42287687231258</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.703178011386616</v>
       </c>
       <c r="E34">
-        <v>-26.7809897954094</v>
+        <v>-24.69439124147311</v>
       </c>
       <c r="F34">
-        <v>4.631614612174741</v>
+        <v>3.720488010845526</v>
       </c>
       <c r="G34">
-        <v>-2.793518929798304</v>
+        <v>-2.906656823602897</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.968332709560105</v>
       </c>
       <c r="E35">
-        <v>-26.3481763636523</v>
+        <v>-24.95878166793694</v>
       </c>
       <c r="F35">
-        <v>4.805950543052231</v>
+        <v>3.303564758958768</v>
       </c>
       <c r="G35">
-        <v>-2.286571780824168</v>
+        <v>-2.001686094987725</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.21233857454018</v>
       </c>
       <c r="E36">
-        <v>-25.56982677968793</v>
+        <v>-24.39456550589927</v>
       </c>
       <c r="F36">
-        <v>5.011046793925301</v>
+        <v>3.936309118177952</v>
       </c>
       <c r="G36">
-        <v>-2.708308798163003</v>
+        <v>-2.454588588033259</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.4332678709163</v>
       </c>
       <c r="E37">
-        <v>-25.2163431555972</v>
+        <v>-24.28906111846856</v>
       </c>
       <c r="F37">
-        <v>4.906123109615606</v>
+        <v>3.264741792147685</v>
       </c>
       <c r="G37">
-        <v>-2.707848632333044</v>
+        <v>-2.782458397151599</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.624001779574751</v>
       </c>
       <c r="E38">
-        <v>-23.59374563390883</v>
+        <v>-23.63805222359988</v>
       </c>
       <c r="F38">
-        <v>4.823143254470241</v>
+        <v>3.666290427007357</v>
       </c>
       <c r="G38">
-        <v>-1.853165090459402</v>
+        <v>-2.897665381918237</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.787811330692489</v>
       </c>
       <c r="E39">
-        <v>-24.53012537531888</v>
+        <v>-22.93732521260098</v>
       </c>
       <c r="F39">
-        <v>4.430851380686313</v>
+        <v>3.025116001200289</v>
       </c>
       <c r="G39">
-        <v>-2.37404632560833</v>
+        <v>-1.256899422835729</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.924115171965914</v>
       </c>
       <c r="E40">
-        <v>-23.08292018042159</v>
+        <v>-21.87137677288347</v>
       </c>
       <c r="F40">
-        <v>4.583739182351007</v>
+        <v>3.592404211228445</v>
       </c>
       <c r="G40">
-        <v>-1.541910909402664</v>
+        <v>-1.821880435113289</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.028817016892331</v>
       </c>
       <c r="E41">
-        <v>-22.47579672716124</v>
+        <v>-22.77125248531769</v>
       </c>
       <c r="F41">
-        <v>4.941726402300601</v>
+        <v>3.370546016946364</v>
       </c>
       <c r="G41">
-        <v>-2.309341713043275</v>
+        <v>-2.808336931632082</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.108668696023157</v>
       </c>
       <c r="E42">
-        <v>-21.83073371866463</v>
+        <v>-19.98105133938763</v>
       </c>
       <c r="F42">
-        <v>4.583675834114389</v>
+        <v>3.234383733454627</v>
       </c>
       <c r="G42">
-        <v>-1.665251904559291</v>
+        <v>-1.992386772567913</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.164390147082405</v>
       </c>
       <c r="E43">
-        <v>-21.91955973632508</v>
+        <v>-20.91074705316235</v>
       </c>
       <c r="F43">
-        <v>4.638517986260141</v>
+        <v>3.662090438919612</v>
       </c>
       <c r="G43">
-        <v>-2.060938239049601</v>
+        <v>-4.066989792935291</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.196910042132151</v>
       </c>
       <c r="E44">
-        <v>-21.74701129121082</v>
+        <v>-20.10296238814812</v>
       </c>
       <c r="F44">
-        <v>4.481232233268273</v>
+        <v>3.348591101840627</v>
       </c>
       <c r="G44">
-        <v>-1.375363984413009</v>
+        <v>-2.620297945001478</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.21576155196153</v>
       </c>
       <c r="E45">
-        <v>-19.47809637372572</v>
+        <v>-20.51510786453422</v>
       </c>
       <c r="F45">
-        <v>4.533154031705955</v>
+        <v>3.371111399958176</v>
       </c>
       <c r="G45">
-        <v>-2.549667455921128</v>
+        <v>-3.388334578475776</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.221250612110039</v>
       </c>
       <c r="E46">
-        <v>-20.25383302818767</v>
+        <v>-19.68305057883887</v>
       </c>
       <c r="F46">
-        <v>4.564926339781501</v>
+        <v>3.579368727838463</v>
       </c>
       <c r="G46">
-        <v>-2.819046546451624</v>
+        <v>-2.86212667555416</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.217945862719955</v>
       </c>
       <c r="E47">
-        <v>-19.90187097136351</v>
+        <v>-19.79076939005933</v>
       </c>
       <c r="F47">
-        <v>4.688959019666887</v>
+        <v>3.270980009748601</v>
       </c>
       <c r="G47">
-        <v>-2.756212392116257</v>
+        <v>-3.407433115691831</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.21458822319096</v>
       </c>
       <c r="E48">
-        <v>-19.08479840615955</v>
+        <v>-17.81259156081468</v>
       </c>
       <c r="F48">
-        <v>4.713192887584942</v>
+        <v>3.094987522483562</v>
       </c>
       <c r="G48">
-        <v>-3.068151856099624</v>
+        <v>-3.338795575026122</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.208679520956296</v>
       </c>
       <c r="E49">
-        <v>-17.75320515267809</v>
+        <v>-17.45673954481793</v>
       </c>
       <c r="F49">
-        <v>3.941278787340601</v>
+        <v>3.080430097708843</v>
       </c>
       <c r="G49">
-        <v>-2.994740508766285</v>
+        <v>-2.830818846389273</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.207740024887973</v>
       </c>
       <c r="E50">
-        <v>-17.07096790105251</v>
+        <v>-16.06091894448568</v>
       </c>
       <c r="F50">
-        <v>4.47179809713</v>
+        <v>2.949392686559467</v>
       </c>
       <c r="G50">
-        <v>-3.084631751794116</v>
+        <v>-2.647676156611251</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.21816315620882</v>
       </c>
       <c r="E51">
-        <v>-17.69251001555328</v>
+        <v>-17.44902302510886</v>
       </c>
       <c r="F51">
-        <v>4.380278899688585</v>
+        <v>2.904016344670296</v>
       </c>
       <c r="G51">
-        <v>-2.349932311900279</v>
+        <v>-2.383590628398049</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.235149329649266</v>
       </c>
       <c r="E52">
-        <v>-15.89572021268587</v>
+        <v>-17.07047882585968</v>
       </c>
       <c r="F52">
-        <v>4.440207915234729</v>
+        <v>3.709468585085898</v>
       </c>
       <c r="G52">
-        <v>-3.173192155515159</v>
+        <v>-2.604701964965972</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.268044061418812</v>
       </c>
       <c r="E53">
-        <v>-17.43837658271683</v>
+        <v>-15.2744181073075</v>
       </c>
       <c r="F53">
-        <v>4.34101249522118</v>
+        <v>3.958742312470152</v>
       </c>
       <c r="G53">
-        <v>-3.031633228255923</v>
+        <v>-2.660398583118671</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.31876159385604</v>
       </c>
       <c r="E54">
-        <v>-15.26474075835311</v>
+        <v>-14.88719735185963</v>
       </c>
       <c r="F54">
-        <v>4.052385259544171</v>
+        <v>3.594413934035138</v>
       </c>
       <c r="G54">
-        <v>-3.535796208431532</v>
+        <v>-4.112039696633693</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.381550510764128</v>
       </c>
       <c r="E55">
-        <v>-14.92085749915864</v>
+        <v>-14.22330041996511</v>
       </c>
       <c r="F55">
-        <v>4.05115947116562</v>
+        <v>2.829583750350558</v>
       </c>
       <c r="G55">
-        <v>-3.993939295065733</v>
+        <v>-3.615788920296942</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.466293598878454</v>
       </c>
       <c r="E56">
-        <v>-14.21759001424144</v>
+        <v>-12.8028222786611</v>
       </c>
       <c r="F56">
-        <v>4.231966424413597</v>
+        <v>3.406188902279244</v>
       </c>
       <c r="G56">
-        <v>-3.029653522023439</v>
+        <v>-3.673700293415413</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.571193911097726</v>
       </c>
       <c r="E57">
-        <v>-15.60402308795579</v>
+        <v>-13.51008387765306</v>
       </c>
       <c r="F57">
-        <v>4.396055778018193</v>
+        <v>3.224341454244825</v>
       </c>
       <c r="G57">
-        <v>-3.188841104279294</v>
+        <v>-3.589052954521788</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.691950079344939</v>
       </c>
       <c r="E58">
-        <v>-14.61349638283603</v>
+        <v>-13.41613615588993</v>
       </c>
       <c r="F58">
-        <v>4.096705269587744</v>
+        <v>3.335509690979097</v>
       </c>
       <c r="G58">
-        <v>-3.763531946623537</v>
+        <v>-4.426799745416519</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.836217973119671</v>
       </c>
       <c r="E59">
-        <v>-13.49659355358421</v>
+        <v>-12.10261151369908</v>
       </c>
       <c r="F59">
-        <v>3.970171918061878</v>
+        <v>3.275354205487045</v>
       </c>
       <c r="G59">
-        <v>-4.454684470493801</v>
+        <v>-4.688200421197372</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.997114013101501</v>
       </c>
       <c r="E60">
-        <v>-13.69533469235884</v>
+        <v>-13.14586324169014</v>
       </c>
       <c r="F60">
-        <v>3.392141430809296</v>
+        <v>3.296776995405195</v>
       </c>
       <c r="G60">
-        <v>-3.769212842768926</v>
+        <v>-4.819509899467024</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.173010723362182</v>
       </c>
       <c r="E61">
-        <v>-12.63369735989663</v>
+        <v>-13.41785244753884</v>
       </c>
       <c r="F61">
-        <v>4.187282162009472</v>
+        <v>3.22403421529723</v>
       </c>
       <c r="G61">
-        <v>-4.402679110617389</v>
+        <v>-4.906597110423093</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.368766800692562</v>
       </c>
       <c r="E62">
-        <v>-13.86507548358835</v>
+        <v>-12.1779607927127</v>
       </c>
       <c r="F62">
-        <v>3.735903804226413</v>
+        <v>3.236643681795959</v>
       </c>
       <c r="G62">
-        <v>-3.931482542921843</v>
+        <v>-4.414431547281802</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.573746727729583</v>
       </c>
       <c r="E63">
-        <v>-13.50090013236551</v>
+        <v>-11.54213587119174</v>
       </c>
       <c r="F63">
-        <v>3.914143570185462</v>
+        <v>3.505838845890525</v>
       </c>
       <c r="G63">
-        <v>-4.229981192015768</v>
+        <v>-3.129837251132864</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.790380443716803</v>
       </c>
       <c r="E64">
-        <v>-13.48712904290818</v>
+        <v>-11.11289540542669</v>
       </c>
       <c r="F64">
-        <v>3.670111909381313</v>
+        <v>3.211049410496542</v>
       </c>
       <c r="G64">
-        <v>-4.876577083472981</v>
+        <v>-4.03528800885123</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.020272504669359</v>
       </c>
       <c r="E65">
-        <v>-13.03232986984384</v>
+        <v>-11.07784954508133</v>
       </c>
       <c r="F65">
-        <v>4.164552814711085</v>
+        <v>3.418006515820253</v>
       </c>
       <c r="G65">
-        <v>-4.191850328494443</v>
+        <v>-4.848490415117804</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.249785441731603</v>
       </c>
       <c r="E66">
-        <v>-12.91660471657782</v>
+        <v>-11.54484389864833</v>
       </c>
       <c r="F66">
-        <v>3.465764751406245</v>
+        <v>3.245838678341</v>
       </c>
       <c r="G66">
-        <v>-4.612054563248596</v>
+        <v>-4.041180779911133</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.48480221864579</v>
       </c>
       <c r="E67">
-        <v>-12.81952329080139</v>
+        <v>-10.75926687016771</v>
       </c>
       <c r="F67">
-        <v>3.728650431133701</v>
+        <v>2.99385839754726</v>
       </c>
       <c r="G67">
-        <v>-4.488892337551089</v>
+        <v>-5.289839104231282</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.722244474051974</v>
       </c>
       <c r="E68">
-        <v>-11.26065498382297</v>
+        <v>-11.2782073490767</v>
       </c>
       <c r="F68">
-        <v>3.88929047325447</v>
+        <v>2.859306742971525</v>
       </c>
       <c r="G68">
-        <v>-4.949412395882486</v>
+        <v>-5.887637554439637</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.949158973674082</v>
       </c>
       <c r="E69">
-        <v>-12.14477613518449</v>
+        <v>-10.54180954831938</v>
       </c>
       <c r="F69">
-        <v>3.477173768821071</v>
+        <v>2.774519879376643</v>
       </c>
       <c r="G69">
-        <v>-5.298499491362016</v>
+        <v>-5.691312272324238</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.171727786953367</v>
       </c>
       <c r="E70">
-        <v>-12.40782160486804</v>
+        <v>-11.19563968249484</v>
       </c>
       <c r="F70">
-        <v>3.487645232333957</v>
+        <v>3.02627527393039</v>
       </c>
       <c r="G70">
-        <v>-5.140030297488182</v>
+        <v>-4.757152463689312</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.383414315907734</v>
       </c>
       <c r="E71">
-        <v>-11.8926261739634</v>
+        <v>-11.47357930318962</v>
       </c>
       <c r="F71">
-        <v>3.53791364179592</v>
+        <v>2.599949560023668</v>
       </c>
       <c r="G71">
-        <v>-4.905547667487143</v>
+        <v>-4.761989170722187</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.574095572776139</v>
       </c>
       <c r="E72">
-        <v>-12.65049799846509</v>
+        <v>-10.99181759588361</v>
       </c>
       <c r="F72">
-        <v>3.45837676331072</v>
+        <v>2.696093178738166</v>
       </c>
       <c r="G72">
-        <v>-4.677705991837882</v>
+        <v>-5.046811956193384</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.749324657620788</v>
       </c>
       <c r="E73">
-        <v>-12.68766771312005</v>
+        <v>-10.8850090079387</v>
       </c>
       <c r="F73">
-        <v>3.457152558638085</v>
+        <v>2.47587570378448</v>
       </c>
       <c r="G73">
-        <v>-4.719293064902207</v>
+        <v>-4.303405781531264</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.898356348570942</v>
       </c>
       <c r="E74">
-        <v>-12.49253123965553</v>
+        <v>-11.43181771589088</v>
       </c>
       <c r="F74">
-        <v>3.322866966656144</v>
+        <v>2.457412860222287</v>
       </c>
       <c r="G74">
-        <v>-5.484512424122585</v>
+        <v>-6.331048713424081</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.015167621694056</v>
       </c>
       <c r="E75">
-        <v>-11.91357036624888</v>
+        <v>-11.11626006161439</v>
       </c>
       <c r="F75">
-        <v>3.493978472289799</v>
+        <v>2.613556761249124</v>
       </c>
       <c r="G75">
-        <v>-4.376257646668466</v>
+        <v>-4.56397551038176</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.10164209703629</v>
       </c>
       <c r="E76">
-        <v>-12.26778307465485</v>
+        <v>-12.01671541872158</v>
       </c>
       <c r="F76">
-        <v>2.929306544433949</v>
+        <v>2.18929461615022</v>
       </c>
       <c r="G76">
-        <v>-3.878073511736781</v>
+        <v>-6.049721864042355</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.143705688398896</v>
       </c>
       <c r="E77">
-        <v>-14.87026991601895</v>
+        <v>-12.04932043157681</v>
       </c>
       <c r="F77">
-        <v>3.154357489841556</v>
+        <v>2.637784294343517</v>
       </c>
       <c r="G77">
-        <v>-3.488597760678143</v>
+        <v>-5.710592889544953</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.140171814030429</v>
       </c>
       <c r="E78">
-        <v>-13.72186249309577</v>
+        <v>-12.71660919050307</v>
       </c>
       <c r="F78">
-        <v>3.13103742023671</v>
+        <v>2.655415692300104</v>
       </c>
       <c r="G78">
-        <v>-3.615338686103601</v>
+        <v>-4.855396213112724</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.091345269927357</v>
       </c>
       <c r="E79">
-        <v>-13.95003418444625</v>
+        <v>-12.16232850043823</v>
       </c>
       <c r="F79">
-        <v>3.239906115981764</v>
+        <v>2.63743587904212</v>
       </c>
       <c r="G79">
-        <v>-4.231288857503781</v>
+        <v>-4.648311657994693</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.98459173442531</v>
       </c>
       <c r="E80">
-        <v>-14.94931895829685</v>
+        <v>-12.31418181933744</v>
       </c>
       <c r="F80">
-        <v>2.86527097944907</v>
+        <v>2.769144781499642</v>
       </c>
       <c r="G80">
-        <v>-3.822327235400993</v>
+        <v>-3.981216868558314</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.828821621410903</v>
       </c>
       <c r="E81">
-        <v>-13.98935039578085</v>
+        <v>-13.63423652104735</v>
       </c>
       <c r="F81">
-        <v>2.861970536321294</v>
+        <v>2.13125337805528</v>
       </c>
       <c r="G81">
-        <v>-3.333015362514554</v>
+        <v>-4.951325891204185</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.62846280219051</v>
       </c>
       <c r="E82">
-        <v>-14.85332889475626</v>
+        <v>-14.42256233325062</v>
       </c>
       <c r="F82">
-        <v>2.90503941869167</v>
+        <v>1.952856825210603</v>
       </c>
       <c r="G82">
-        <v>-2.955960778319263</v>
+        <v>-4.641836230919879</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.380382615364244</v>
       </c>
       <c r="E83">
-        <v>-16.01743200859002</v>
+        <v>-15.67468086789747</v>
       </c>
       <c r="F83">
-        <v>3.125907796776602</v>
+        <v>2.032805467233817</v>
       </c>
       <c r="G83">
-        <v>-2.821493039605146</v>
+        <v>-3.330840334095253</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.104215760784863</v>
       </c>
       <c r="E84">
-        <v>-16.24554030130439</v>
+        <v>-15.33401735372245</v>
       </c>
       <c r="F84">
-        <v>2.967012998574647</v>
+        <v>1.85959713496812</v>
       </c>
       <c r="G84">
-        <v>-3.183583957962932</v>
+        <v>-3.807754213937121</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.80913582829798</v>
       </c>
       <c r="E85">
-        <v>-17.2773576324261</v>
+        <v>-15.55424157318947</v>
       </c>
       <c r="F85">
-        <v>2.632543811469328</v>
+        <v>2.473926161802575</v>
       </c>
       <c r="G85">
-        <v>-2.568014499299768</v>
+        <v>-4.273802883319101</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.5006681053617</v>
       </c>
       <c r="E86">
-        <v>-19.02411685445676</v>
+        <v>-17.06979049781052</v>
       </c>
       <c r="F86">
-        <v>2.924813570751847</v>
+        <v>1.897192729694737</v>
       </c>
       <c r="G86">
-        <v>-2.049371192935387</v>
+        <v>-1.814540955652725</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.203267420030238</v>
       </c>
       <c r="E87">
-        <v>-19.52588535992867</v>
+        <v>-18.68917733142744</v>
       </c>
       <c r="F87">
-        <v>2.676529659564743</v>
+        <v>1.932510955314952</v>
       </c>
       <c r="G87">
-        <v>-2.114244643322945</v>
+        <v>-3.181564525183976</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.924319186414143</v>
       </c>
       <c r="E88">
-        <v>-19.98874068825265</v>
+        <v>-20.15776598058895</v>
       </c>
       <c r="F88">
-        <v>2.928112430173707</v>
+        <v>2.021936493536156</v>
       </c>
       <c r="G88">
-        <v>-1.605791196128441</v>
+        <v>-2.723481028369483</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.674839981388513</v>
       </c>
       <c r="E89">
-        <v>-22.26396829850445</v>
+        <v>-22.61736135311503</v>
       </c>
       <c r="F89">
-        <v>2.479891981986035</v>
+        <v>1.572181434316423</v>
       </c>
       <c r="G89">
-        <v>-1.58317354900414</v>
+        <v>-1.979545166421079</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.475404764491106</v>
       </c>
       <c r="E90">
-        <v>-23.73286941237248</v>
+        <v>-21.35735874522083</v>
       </c>
       <c r="F90">
-        <v>2.505860007881496</v>
+        <v>1.803019241139046</v>
       </c>
       <c r="G90">
-        <v>-1.213806051551036</v>
+        <v>-2.257985220092561</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.326611233565032</v>
       </c>
       <c r="E91">
-        <v>-25.4527928974337</v>
+        <v>-24.96947792354306</v>
       </c>
       <c r="F91">
-        <v>1.99868610699159</v>
+        <v>1.769045581841039</v>
       </c>
       <c r="G91">
-        <v>-1.042568083532234</v>
+        <v>-2.115251049166884</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.239660176188337</v>
       </c>
       <c r="E92">
-        <v>-27.05076910594236</v>
+        <v>-26.82521487256831</v>
       </c>
       <c r="F92">
-        <v>2.149961696034365</v>
+        <v>1.471361132033632</v>
       </c>
       <c r="G92">
-        <v>-1.499244598492537</v>
+        <v>-1.915535768419271</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.224892684139909</v>
       </c>
       <c r="E93">
-        <v>-29.60339292000801</v>
+        <v>-27.28996310302751</v>
       </c>
       <c r="F93">
-        <v>1.616704158717172</v>
+        <v>1.082662686971836</v>
       </c>
       <c r="G93">
-        <v>-1.684608664327409</v>
+        <v>-3.253942982309062</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.270825700624856</v>
       </c>
       <c r="E94">
-        <v>-30.47238670394692</v>
+        <v>-29.8919087917477</v>
       </c>
       <c r="F94">
-        <v>1.489542075942877</v>
+        <v>0.8191292715249656</v>
       </c>
       <c r="G94">
-        <v>-2.07025411419711</v>
+        <v>-2.725325002234857</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.383560809894962</v>
       </c>
       <c r="E95">
-        <v>-32.77932042496342</v>
+        <v>-30.25773477174634</v>
       </c>
       <c r="F95">
-        <v>1.398127403091881</v>
+        <v>0.9064453134668041</v>
       </c>
       <c r="G95">
-        <v>-2.699539163029474</v>
+        <v>-3.427326183837312</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.562830826197252</v>
       </c>
       <c r="E96">
-        <v>-34.52740422564133</v>
+        <v>-35.0763277309551</v>
       </c>
       <c r="F96">
-        <v>1.140534468533824</v>
+        <v>0.3369327884804131</v>
       </c>
       <c r="G96">
-        <v>-1.893295523486447</v>
+        <v>-2.022214787876746</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.787256980661065</v>
       </c>
       <c r="E97">
-        <v>-36.37902705603062</v>
+        <v>-35.62980235264658</v>
       </c>
       <c r="F97">
-        <v>1.050830198071503</v>
+        <v>0.312500165469971</v>
       </c>
       <c r="G97">
-        <v>-2.345529286333048</v>
+        <v>-3.599004454412837</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.070791085702234</v>
       </c>
       <c r="E98">
-        <v>-38.41144241846514</v>
+        <v>-35.9794435665418</v>
       </c>
       <c r="F98">
-        <v>0.9895787880859671</v>
+        <v>0.1604818183528539</v>
       </c>
       <c r="G98">
-        <v>-2.478603285375133</v>
+        <v>-3.567895257980306</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.392174379806772</v>
       </c>
       <c r="E99">
-        <v>-41.72110255357806</v>
+        <v>-39.36101586889653</v>
       </c>
       <c r="F99">
-        <v>0.753565430331688</v>
+        <v>-0.1771476539067242</v>
       </c>
       <c r="G99">
-        <v>-3.579091522994121</v>
+        <v>-3.937464698711306</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.759630492640826</v>
       </c>
       <c r="E100">
-        <v>-42.68983824177291</v>
+        <v>-42.45366700108789</v>
       </c>
       <c r="F100">
-        <v>0.3473361526389348</v>
+        <v>-0.08483343609575882</v>
       </c>
       <c r="G100">
-        <v>-2.186656205903424</v>
+        <v>-2.389178829268339</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.144971217541176</v>
       </c>
       <c r="E101">
-        <v>-45.04961019751091</v>
+        <v>-44.51922626478454</v>
       </c>
       <c r="F101">
-        <v>0.5333709191137758</v>
+        <v>-1.413174691200173</v>
       </c>
       <c r="G101">
-        <v>-3.115386719853945</v>
+        <v>-2.899221338321694</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.597117013043212</v>
       </c>
       <c r="E102">
-        <v>-46.71190658658752</v>
+        <v>-45.5558618922504</v>
       </c>
       <c r="F102">
-        <v>0.03310910269180543</v>
+        <v>-1.332438947336985</v>
       </c>
       <c r="G102">
-        <v>-3.528115742780424</v>
+        <v>-4.306269403422734</v>
       </c>
     </row>
   </sheetData>
